--- a/public/Database_Template.xlsx
+++ b/public/Database_Template.xlsx
@@ -115,7 +115,7 @@
     <t>hisyamagung20@gmail.com</t>
   </si>
   <si>
-    <t>Telecomunications</t>
+    <t>telecommunications</t>
   </si>
   <si>
     <t>100-1000</t>

--- a/public/Database_Template.xlsx
+++ b/public/Database_Template.xlsx
@@ -660,172 +660,10 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M3" s="7">
-        <f>6288271102849</f>
-        <v>6288271102849</v>
-      </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="U3" s="9"/>
-      <c r="V3" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="7">
-        <f>62895606464710</f>
-        <v>62895606464710</v>
-      </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="U4" s="9"/>
-      <c r="V4" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="7">
-        <v>6.285645123565E12</v>
-      </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="U5" s="9"/>
-      <c r="V5" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="T2"/>
     <hyperlink r:id="rId2" ref="V2"/>
-    <hyperlink r:id="rId3" ref="T3"/>
-    <hyperlink r:id="rId4" ref="V3"/>
-    <hyperlink r:id="rId5" ref="T4"/>
-    <hyperlink r:id="rId6" ref="V4"/>
-    <hyperlink r:id="rId7" ref="T5"/>
-    <hyperlink r:id="rId8" ref="V5"/>
   </hyperlinks>
   <drawing r:id="rId9"/>
 </worksheet>

--- a/public/Database_Template.xlsx
+++ b/public/Database_Template.xlsx
@@ -85,7 +85,7 @@
     <t xml:space="preserve"> Astra Daihatsu Motor PT</t>
   </si>
   <si>
-    <t>Mr/Ms/Mrs</t>
+    <t>Ms</t>
   </si>
   <si>
     <t>Jasmine</t>

--- a/public/Database_Template.xlsx
+++ b/public/Database_Template.xlsx
@@ -425,7 +425,7 @@
         <v>Position</v>
       </c>
       <c r="I1" t="str">
-        <v>Speciality/Division</v>
+        <v>Division</v>
       </c>
       <c r="J1" t="str">
         <v>Jobtitle</v>
